--- a/sources/table_normalization/xlsx/education-table15.xlsx
+++ b/sources/table_normalization/xlsx/education-table15.xlsx
@@ -179,14 +179,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -668,7 +668,7 @@
   <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -685,13 +685,13 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>2012</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
@@ -1408,13 +1408,13 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>2013</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
@@ -2131,13 +2131,13 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>2014</v>
       </c>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
@@ -2854,13 +2854,13 @@
       </c>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>2015</v>
       </c>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
